--- a/Junk CSV.xlsx
+++ b/Junk CSV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fd01cd90834395ed/Documents/Personal Classwork/Whole-Rock-Geochemistry-plotting-tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD93E943-F6AC-4788-ACF8-B6833AEC1EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{FD93E943-F6AC-4788-ACF8-B6833AEC1EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{772D05FF-257C-4A85-80CD-0591EB2B179E}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="700" windowWidth="19200" windowHeight="11170" xr2:uid="{9B077DAD-D7AE-4A91-98AB-58FE96AABD7F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>r</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>t</t>
+  </si>
+  <si>
+    <t>yeah yeah</t>
   </si>
 </sst>
 </file>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542439E0-042A-4EDC-9A22-5C78D837F202}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -462,6 +465,11 @@
         <v>3</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
